--- a/output/problem2_stats.xlsx
+++ b/output/problem2_stats.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.5924</v>
+        <v>0.7009</v>
       </c>
     </row>
     <row r="3">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.5347</v>
+        <v>0.6452</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.5719</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.5725</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.5239</v>
+        <v>0.6752</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.4984</v>
+        <v>0.6716</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.7542</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.5598</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6054</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="8">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.5706</v>
+        <v>0.6028</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.6304</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.5664</v>
+        <v>0.5802</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.5935</v>
+        <v>0.5988</v>
       </c>
     </row>
   </sheetData>
@@ -706,25 +706,25 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.1952</v>
+        <v>0.3601</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.0333</v>
+        <v>0.4167</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.8183</v>
+        <v>-0.2011</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.653</v>
+        <v>0.8858</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.6102</v>
+        <v>0.3358</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5239</v>
+        <v>0.6752</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1952</v>
+        <v>0.3601</v>
       </c>
     </row>
     <row r="3">
@@ -734,25 +734,25 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.2946</v>
+        <v>0.2902</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.0833</v>
+        <v>0.4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.913</v>
+        <v>-0.3125</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7578</v>
+        <v>0.8304</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4233</v>
+        <v>0.4488</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.4984</v>
+        <v>0.6716</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2946</v>
+        <v>0.2902</v>
       </c>
     </row>
     <row r="4">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.5534</v>
+        <v>0.1622</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.35</v>
+        <v>0.1833</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.9767</v>
+        <v>-0.2944</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3224</v>
+        <v>0.826</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1534</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7542</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.5534</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="5">
@@ -790,25 +790,25 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.2258</v>
+        <v>-0.0015</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.3833</v>
+        <v>-0.0667</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.8349</v>
+        <v>-0.7924</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4084</v>
+        <v>0.766</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.995</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5598</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2258</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="6">
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.4035</v>
+        <v>0.1644</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2833</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.9172</v>
+        <v>-0.3941</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7275</v>
+        <v>0.7139</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.2979</v>
+        <v>0.6812</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6054</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4035</v>
+        <v>0.1644</v>
       </c>
     </row>
     <row r="7">
@@ -846,25 +846,25 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.348</v>
+        <v>0.0599</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.7923</v>
+        <v>-0.536</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8038</v>
+        <v>0.5951</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.3748</v>
+        <v>0.8726</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6167</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.348</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="8">
@@ -874,25 +874,25 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.3898</v>
+        <v>-0.4141</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.4333</v>
+        <v>-0.55</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.1885</v>
+        <v>-0.8328</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7851</v>
+        <v>-0.0327</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2399</v>
+        <v>0.2734</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5706</v>
+        <v>0.6028</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.3898</v>
+        <v>0.4141</v>
       </c>
     </row>
     <row r="9">
@@ -902,25 +902,25 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.3853</v>
+        <v>-0.336</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.3167</v>
+        <v>-0.3333</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.9045</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8387</v>
+        <v>0.4797</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.3163</v>
+        <v>0.3643</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6304</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.3853</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="10">
@@ -930,25 +930,25 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.209</v>
+        <v>-0.5001</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.1167</v>
+        <v>-0.4333</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.8756</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7554</v>
+        <v>0.3715</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.1599</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.5664</v>
+        <v>0.5802</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.209</v>
+        <v>0.5001</v>
       </c>
     </row>
     <row r="11">
@@ -958,25 +958,25 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1905</v>
+        <v>-0.2694</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.2167</v>
+        <v>-0.2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-0.5716</v>
+        <v>-0.8817</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.6554</v>
+        <v>0.6098</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.6137</v>
+        <v>0.4773</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5935</v>
+        <v>0.5988</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.1905</v>
+        <v>0.2694</v>
       </c>
     </row>
   </sheetData>
@@ -1048,85 +1048,85 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>章节完整度</t>
+          <t>连词密度(连词数/总字符)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.5534</v>
+        <v>-0.5001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.4333</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.9767</v>
+        <v>-0.8756</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3224</v>
+        <v>0.3715</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1534</v>
+        <v>0.1599</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7542</v>
+        <v>0.5802</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.5534</v>
+        <v>0.5001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>公式总数</t>
+          <t>规范编号公式占比</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.4035</v>
+        <v>-0.4141</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.55</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.9172</v>
+        <v>-0.8328</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7275</v>
+        <v>-0.0327</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2979</v>
+        <v>0.2734</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6028</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4035</v>
+        <v>0.4141</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>规范编号公式占比</t>
+          <t>总页数</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.3898</v>
+        <v>0.3601</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.4333</v>
+        <v>0.4167</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.1885</v>
+        <v>-0.2011</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7851</v>
+        <v>0.8858</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.2399</v>
+        <v>0.3358</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.5706</v>
+        <v>0.6752</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3898</v>
+        <v>0.3601</v>
       </c>
     </row>
     <row r="5">
@@ -1136,193 +1136,193 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3853</v>
+        <v>-0.336</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.3167</v>
+        <v>-0.3333</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.9045</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.8387</v>
+        <v>0.4797</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.3163</v>
+        <v>0.3643</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6304</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.3853</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>公式密度(公式数/总字符)</t>
+          <t>总字符数</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.348</v>
+        <v>0.2902</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.7923</v>
+        <v>-0.3125</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8038</v>
+        <v>0.8304</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.3748</v>
+        <v>0.4488</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6716</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.348</v>
+        <v>0.2902</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>总字符数</t>
+          <t>参考文献数量</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.2946</v>
+        <v>-0.2694</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.0833</v>
+        <v>-0.2</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.913</v>
+        <v>-0.8817</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7578</v>
+        <v>0.6098</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4233</v>
+        <v>0.4773</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.4984</v>
+        <v>0.5988</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2946</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>段落平均长度</t>
+          <t>公式总数</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.2258</v>
+        <v>0.1644</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.3833</v>
+        <v>0.2833</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.8349</v>
+        <v>-0.3941</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.4084</v>
+        <v>0.7139</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.6812</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5598</v>
+        <v>0.6054</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2258</v>
+        <v>0.1644</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>连词密度(连词数/总字符)</t>
+          <t>章节完整度</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.209</v>
+        <v>0.1622</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.1167</v>
+        <v>0.1833</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.2944</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7554</v>
+        <v>0.826</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.5664</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.209</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>总页数</t>
+          <t>公式密度(公式数/总字符)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.1952</v>
+        <v>0.0599</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.0333</v>
+        <v>0.0667</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-0.8183</v>
+        <v>-0.536</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.653</v>
+        <v>0.5951</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.6102</v>
+        <v>0.8726</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.5239</v>
+        <v>0.6167</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.1952</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>参考文献数量</t>
+          <t>段落平均长度</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1905</v>
+        <v>-0.0015</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.2167</v>
+        <v>-0.0667</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-0.5716</v>
+        <v>-0.7924</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.6554</v>
+        <v>0.766</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.6137</v>
+        <v>0.995</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5935</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.1905</v>
+        <v>0.0015</v>
       </c>
     </row>
   </sheetData>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2746</v>
+        <v>-0.2186</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6.3797</v>
+        <v>-2.1782</v>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.21</v>
+        <v>-0.2519</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6.464</v>
+        <v>-3.3242</v>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
     </row>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1862</v>
+        <v>-0.2467</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5.6021</v>
+        <v>-3.182</v>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>62.8351</v>
+        <v>71.5177</v>
       </c>
     </row>
     <row r="6">
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2403</v>
+        <v>0.2633</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.8716</v>
+        <v>0.8583</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6788</v>
+        <v>0.6953</v>
       </c>
     </row>
     <row r="7">
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.0617</v>
+        <v>-1.2261</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12.7592</v>
+        <v>5.6859</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10.6119</v>
+        <v>4.6596</v>
       </c>
     </row>
     <row r="8">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.4152</v>
+        <v>-1.6651</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>75.89</v>
+        <v>66.64</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>64.56</v>
+        <v>69.39</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>65.17</v>
+        <v>69.28</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.72</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="3">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>47.61</v>
+        <v>71.2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>71.66</v>
+        <v>69.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-24.05</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>79.58</v>
+        <v>73.7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>63.1</v>
+        <v>62.68</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>64.73</v>
+        <v>63.89</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14.85</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="5">
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>64.31</v>
+        <v>62.44</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>74.31</v>
+        <v>73.77</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>73.59</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-9.27</v>
+        <v>-10.42</v>
       </c>
     </row>
     <row r="6">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69.94</v>
+        <v>67.12</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>67.72</v>
+        <v>69.59</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>67.77</v>
+        <v>69.48</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.17</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="7">
@@ -1620,16 +1620,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>70.73</v>
+        <v>74.31</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>53.31</v>
+        <v>67.13</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>56.49</v>
+        <v>67.45</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.23</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="8">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>74</v>
+        <v>65.39</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>68.09</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>70.45</v>
+        <v>68.08</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.55</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="9">
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>74.20999999999999</v>
+        <v>65.23</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>92.06</v>
+        <v>62.5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>89.84</v>
+        <v>62.99</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-15.63</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="10">
@@ -1677,16 +1677,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>74.06</v>
+        <v>67.44</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>75.94</v>
+        <v>63.32</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>75.09</v>
+        <v>63.93</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1.03</v>
+        <v>3.51</v>
       </c>
     </row>
   </sheetData>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2577</v>
+        <v>-0.1512</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.6857</v>
+        <v>-0.9657</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.9314</v>
+        <v>0.6217</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.4237</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="3">
@@ -1763,16 +1763,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2765</v>
+        <v>-0.2864</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.4235</v>
+        <v>-0.9136</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.9964</v>
+        <v>0.3646</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3494</v>
+        <v>0.3399</v>
       </c>
     </row>
     <row r="4">
@@ -1782,16 +1782,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1878</v>
+        <v>-0.1956</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.4823</v>
+        <v>-0.8298</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.7454</v>
+        <v>0.7071</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3051</v>
+        <v>0.3623</v>
       </c>
     </row>
   </sheetData>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>50.5</v>
+        <v>32.9</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>31.1</v>
+        <v>15.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30</v>
+        <v>14.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="3">
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>22.9</v>
+        <v>1.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>111.8</v>
+        <v>236</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>119.6</v>
+        <v>147.3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>26.6</v>
+        <v>12.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>119.6</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46.6</v>
+        <v>179</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>49.6</v>
+        <v>139.1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>50.1</v>
+        <v>112.4</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>50.1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7.5</v>
+        <v>23.3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>21.3</v>
+        <v>34.1</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>21.3</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="7">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>73.7</v>
+        <v>125.3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>29.3</v>
+        <v>47.4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>113.4</v>
+        <v>123.6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>113.4</v>
+        <v>125.3</v>
       </c>
     </row>
     <row r="8">
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.4</v>
+        <v>16.9</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>17</v>
+        <v>23.2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="9">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>38.4</v>
+        <v>8.4</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="10">
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.2</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13.1</v>
+        <v>32.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.1</v>
+        <v>32.7</v>
       </c>
     </row>
   </sheetData>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>75.89</v>
+        <v>66.64</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>65.17</v>
+        <v>69.28</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.726</v>
@@ -2098,7 +2098,7 @@
         <v>1.0201</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>77.42</v>
+        <v>67.98</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>47.61</v>
+        <v>71.2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>71.66</v>
+        <v>69.8</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.6761</v>
@@ -2130,16 +2130,16 @@
         <v>1.0118</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>48.18</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>及格</t>
+          <t>良好</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>及格</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>79.58</v>
+        <v>73.7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>64.73</v>
+        <v>63.89</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.5563</v>
@@ -2162,7 +2162,7 @@
         <v>0.992</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>78.94</v>
+        <v>73.11</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>64.31</v>
+        <v>62.44</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>73.59</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.5818</v>
@@ -2194,7 +2194,7 @@
         <v>0.9962</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69.94</v>
+        <v>67.12</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>67.77</v>
+        <v>69.48</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.488</v>
@@ -2226,7 +2226,7 @@
         <v>0.9807</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>68.59</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>70.73</v>
+        <v>74.31</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>56.49</v>
+        <v>67.45</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.5075</v>
@@ -2258,7 +2258,7 @@
         <v>0.9839</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>69.59</v>
+        <v>73.12</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>74</v>
+        <v>65.39</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>70.45</v>
+        <v>68.08</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.5689</v>
@@ -2290,7 +2290,7 @@
         <v>0.9941</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>73.56999999999999</v>
+        <v>65</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>74.20999999999999</v>
+        <v>65.23</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>89.84</v>
+        <v>62.99</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.6632</v>
@@ -2322,7 +2322,7 @@
         <v>1.0097</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>74.93000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>74.06</v>
+        <v>67.44</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>75.09</v>
+        <v>63.93</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.674</v>
@@ -2354,7 +2354,7 @@
         <v>1.0115</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>74.91</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>

--- a/output/problem2_stats.xlsx
+++ b/output/problem2_stats.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.7009</v>
+        <v>0.6999</v>
       </c>
     </row>
     <row r="3">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.6452</v>
+        <v>0.6516999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6281</v>
       </c>
     </row>
     <row r="5">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6012</v>
       </c>
     </row>
   </sheetData>
@@ -536,21 +536,21 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>总页数</t>
+          <t>内容页数</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.6752</v>
+        <v>0.6589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>总字符数</t>
+          <t>内容字符数</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.6716</v>
+        <v>0.7493</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6129</v>
       </c>
     </row>
     <row r="5">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6778999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -580,17 +580,17 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.6054</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>公式密度(公式数/总字符)</t>
+          <t>公式密度(公式数/内容字符)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.6167</v>
+        <v>0.6197</v>
       </c>
     </row>
     <row r="8">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.6028</v>
+        <v>0.6001</v>
       </c>
     </row>
     <row r="9">
@@ -610,17 +610,17 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6098</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>连词密度(连词数/总字符)</t>
+          <t>连词密度(连词数/内容字符)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.5802</v>
+        <v>0.6068</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.5988</v>
+        <v>0.5995</v>
       </c>
     </row>
   </sheetData>
@@ -702,57 +702,57 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>总页数</t>
+          <t>内容页数</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.3601</v>
+        <v>0.4155</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.1333</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.2011</v>
+        <v>-0.5269</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.8858</v>
+        <v>0.8806</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.3358</v>
+        <v>0.2709</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6752</v>
+        <v>0.6589</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3601</v>
+        <v>0.4155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>总字符数</t>
+          <t>内容字符数</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2902</v>
+        <v>0.4341</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.4</v>
+        <v>0.4167</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.3125</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8304</v>
+        <v>0.9233</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4488</v>
+        <v>0.2424</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.6716</v>
+        <v>0.7493</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2902</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="4">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1622</v>
+        <v>-0.0582</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.1833</v>
+        <v>-0.2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.2944</v>
+        <v>-0.8776</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.826</v>
+        <v>0.6567</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.8656</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6129</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1622</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="5">
@@ -790,25 +790,25 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.0015</v>
+        <v>-0.0012</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.0667</v>
+        <v>0.0167</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.7924</v>
+        <v>-0.7855</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.766</v>
+        <v>0.7532</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.995</v>
+        <v>0.997</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="6">
@@ -818,53 +818,53 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.1644</v>
+        <v>0.1785</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.2833</v>
+        <v>0.2667</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.3941</v>
+        <v>-0.3747</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7139</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6812</v>
+        <v>0.6582</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6054</v>
+        <v>0.643</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1644</v>
+        <v>0.1785</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>公式密度(公式数/总字符)</t>
+          <t>公式密度(公式数/内容字符)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.0599</v>
+        <v>0.0369</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.0667</v>
+        <v>0.0167</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.536</v>
+        <v>-0.4173</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5951</v>
+        <v>0.6108</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8726</v>
+        <v>0.9275</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6167</v>
+        <v>0.6197</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0599</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="8">
@@ -874,25 +874,25 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.4141</v>
+        <v>0.0599</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.0833</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.8328</v>
+        <v>-0.7088</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.0327</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2734</v>
+        <v>0.8631</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6028</v>
+        <v>0.6001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4141</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="9">
@@ -902,53 +902,53 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.336</v>
+        <v>-0.3689</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.3333</v>
+        <v>-0.4167</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-0.9045</v>
+        <v>-0.9085</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.4797</v>
+        <v>0.4542</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.3643</v>
+        <v>0.3163</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6098</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.336</v>
+        <v>0.3689</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>连词密度(连词数/总字符)</t>
+          <t>连词密度(连词数/内容字符)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.5001</v>
+        <v>-0.3976</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.4333</v>
+        <v>-0.65</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-0.8756</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.3715</v>
+        <v>0.5163</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1599</v>
+        <v>0.2889</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.5802</v>
+        <v>0.6068</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.5001</v>
+        <v>0.3976</v>
       </c>
     </row>
     <row r="11">
@@ -958,25 +958,25 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.2694</v>
+        <v>-0.3369</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-0.8817</v>
+        <v>-0.9115</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.6098</v>
+        <v>0.4533</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.4773</v>
+        <v>0.3678</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5988</v>
+        <v>0.5995</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.2694</v>
+        <v>0.3369</v>
       </c>
     </row>
   </sheetData>
@@ -1048,85 +1048,85 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>连词密度(连词数/总字符)</t>
+          <t>内容字符数</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.5001</v>
+        <v>0.4341</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.4333</v>
+        <v>0.4167</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.8756</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3715</v>
+        <v>0.9233</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1599</v>
+        <v>0.2424</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.5802</v>
+        <v>0.7493</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.5001</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>规范编号公式占比</t>
+          <t>内容页数</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.4141</v>
+        <v>0.4155</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.55</v>
+        <v>0.1333</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.8328</v>
+        <v>-0.5269</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.0327</v>
+        <v>0.8806</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2734</v>
+        <v>0.2709</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.6028</v>
+        <v>0.6589</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4141</v>
+        <v>0.4155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>总页数</t>
+          <t>连词密度(连词数/内容字符)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.3601</v>
+        <v>-0.3976</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.4167</v>
+        <v>-0.65</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.2011</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8858</v>
+        <v>0.5163</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3358</v>
+        <v>0.2889</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6752</v>
+        <v>0.6068</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3601</v>
+        <v>0.3976</v>
       </c>
     </row>
     <row r="5">
@@ -1136,109 +1136,109 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.336</v>
+        <v>-0.3689</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.3333</v>
+        <v>-0.4167</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.9045</v>
+        <v>-0.9085</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4797</v>
+        <v>0.4542</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.3643</v>
+        <v>0.3163</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6098</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.336</v>
+        <v>0.3689</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>总字符数</t>
+          <t>参考文献数量</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2902</v>
+        <v>-0.3369</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.3125</v>
+        <v>-0.9115</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8304</v>
+        <v>0.4533</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.4488</v>
+        <v>0.3678</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6716</v>
+        <v>0.5995</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2902</v>
+        <v>0.3369</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>参考文献数量</t>
+          <t>公式总数</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.2694</v>
+        <v>0.1785</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.2667</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.8817</v>
+        <v>-0.3747</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6098</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4773</v>
+        <v>0.6582</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5988</v>
+        <v>0.643</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2694</v>
+        <v>0.1785</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>公式总数</t>
+          <t>规范编号公式占比</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1644</v>
+        <v>0.0599</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.2833</v>
+        <v>-0.0833</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.3941</v>
+        <v>-0.7088</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7139</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6812</v>
+        <v>0.8631</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6054</v>
+        <v>0.6001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1644</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="9">
@@ -1248,53 +1248,53 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.1622</v>
+        <v>-0.0582</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.1833</v>
+        <v>-0.2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-0.2944</v>
+        <v>-0.8776</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.826</v>
+        <v>0.6567</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.8656</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6129</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.1622</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>公式密度(公式数/总字符)</t>
+          <t>公式密度(公式数/内容字符)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.0599</v>
+        <v>0.0369</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.0667</v>
+        <v>0.0167</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-0.536</v>
+        <v>-0.4173</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.5951</v>
+        <v>0.6108</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8726</v>
+        <v>0.9275</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6167</v>
+        <v>0.6197</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.0599</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="11">
@@ -1304,25 +1304,25 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.0015</v>
+        <v>-0.0012</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.0667</v>
+        <v>0.0167</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-0.7924</v>
+        <v>-0.7855</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.766</v>
+        <v>0.7532</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.995</v>
+        <v>0.997</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.0015</v>
+        <v>0.0012</v>
       </c>
     </row>
   </sheetData>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.2186</v>
+        <v>-0.3207</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-2.1782</v>
+        <v>-3.2742</v>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.2519</v>
+        <v>0.1498</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-3.3242</v>
+        <v>1.4528</v>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
     </row>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.2467</v>
+        <v>-0.3366</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-3.182</v>
+        <v>-3.8094</v>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>71.5177</v>
+        <v>69.9803</v>
       </c>
     </row>
     <row r="6">
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2633</v>
+        <v>0.2672</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.8583</v>
+        <v>0.856</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6953</v>
+        <v>0.6894</v>
       </c>
     </row>
     <row r="7">
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.2261</v>
+        <v>-0.9193</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5.6859</v>
+        <v>5.1398</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4.6596</v>
+        <v>4.2737</v>
       </c>
     </row>
     <row r="8">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.6651</v>
+        <v>-1.0967</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>66.64</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>69.39</v>
+        <v>69.53</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>69.28</v>
+        <v>69.33</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-2.64</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="3">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>71.2</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>69.8</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="4">
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>73.7</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>62.68</v>
+        <v>62.34</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>63.89</v>
+        <v>62.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.81</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="5">
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>62.44</v>
+        <v>61.14</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>73.77</v>
+        <v>69.72</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>72.84999999999999</v>
+        <v>69.56</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-10.42</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="6">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>67.12</v>
+        <v>67.66</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>69.59</v>
+        <v>63.3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>69.48</v>
+        <v>64.19</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-2.36</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="7">
@@ -1620,16 +1620,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>74.31</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>67.13</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>67.45</v>
+        <v>67.11</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.86</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="8">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>65.39</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>68.09</v>
+        <v>66.92</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>68.08</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.69</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="9">
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>65.23</v>
+        <v>64.89</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>62.5</v>
+        <v>67.22</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>62.99</v>
+        <v>67.13</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.24</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="10">
@@ -1677,16 +1677,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>67.44</v>
+        <v>66.39</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>63.32</v>
+        <v>64.42</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>63.93</v>
+        <v>64.84</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.51</v>
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.1512</v>
+        <v>-0.2136</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.9657</v>
+        <v>-0.8472</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6217</v>
+        <v>0.491</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.457</v>
+        <v>0.3831</v>
       </c>
     </row>
     <row r="3">
@@ -1763,16 +1763,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.2864</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.9136</v>
+        <v>-0.6096</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.3646</v>
+        <v>0.584</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3399</v>
+        <v>0.3121</v>
       </c>
     </row>
     <row r="4">
@@ -1782,16 +1782,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.1956</v>
+        <v>-0.2683</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.8298</v>
+        <v>-0.8953</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.7071</v>
+        <v>0.6111</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3623</v>
+        <v>0.3553</v>
       </c>
     </row>
   </sheetData>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>32.9</v>
+        <v>31.1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>15.8</v>
+        <v>6.9</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14.8</v>
+        <v>13.6</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.9</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="3">
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7.4</v>
+        <v>13.3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.8</v>
+        <v>10.4</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="4">
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>236</v>
+        <v>103.2</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>147.3</v>
+        <v>128.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12.9</v>
+        <v>33.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>236</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="5">
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>179</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>139.1</v>
+        <v>92.7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>112.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>179</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="6">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>23.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34.1</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>125.3</v>
+        <v>47.2</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>47.4</v>
+        <v>186.2</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>123.6</v>
+        <v>79.5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>125.3</v>
+        <v>186.2</v>
       </c>
     </row>
     <row r="8">
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>16.9</v>
+        <v>1.8</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>23.2</v>
+        <v>35.6</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>23.2</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="9">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.3</v>
+        <v>35.1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7.9</v>
+        <v>39.1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8.4</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="10">
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>16</v>
+        <v>0.8</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.6</v>
+        <v>47.6</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32.7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32.7</v>
+        <v>47.6</v>
       </c>
     </row>
   </sheetData>
@@ -2086,19 +2086,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>66.64</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>69.28</v>
+        <v>69.33</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.726</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.0201</v>
+        <v>1.0109</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>67.98</v>
+        <v>65.89</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2118,19 +2118,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>71.2</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>69.8</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.6761</v>
+        <v>0.4376</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.0118</v>
+        <v>0.9787</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>72.04000000000001</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2150,19 +2150,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>73.7</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>63.89</v>
+        <v>62.9</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.5563</v>
+        <v>0.5476</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.992</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>73.11</v>
+        <v>72.13</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2182,19 +2182,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>62.44</v>
+        <v>61.14</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>72.84999999999999</v>
+        <v>69.56</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5818</v>
+        <v>0.5522</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9962</v>
+        <v>0.9993</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>62.2</v>
+        <v>61.1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>67.12</v>
+        <v>67.66</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>69.48</v>
+        <v>64.19</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.488</v>
+        <v>0.4859</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9807</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65.81999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2246,19 +2246,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>74.31</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>67.45</v>
+        <v>67.11</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.5075</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9839</v>
+        <v>1.0101</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>73.12</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2278,19 +2278,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>65.39</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>68.08</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.5689</v>
+        <v>0.4765</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9941</v>
+        <v>0.9857</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65</v>
+        <v>64.25</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -2310,23 +2310,23 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>65.23</v>
+        <v>64.89</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>62.99</v>
+        <v>67.13</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.6632</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.0097</v>
+        <v>1.0147</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>65.86</v>
+        <v>65.84</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>67.44</v>
+        <v>66.39</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>63.93</v>
+        <v>64.84</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.674</v>
+        <v>0.6384</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.0115</v>
+        <v>1.0148</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>68.20999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>

--- a/output/problem2_stats.xlsx
+++ b/output/problem2_stats.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.6999</v>
+        <v>0.6423</v>
       </c>
     </row>
     <row r="3">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6518</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.6281</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="5">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.6012</v>
+        <v>0.5273</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.6589</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.7493</v>
+        <v>0.7097</v>
       </c>
     </row>
     <row r="4">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.6129</v>
+        <v>0.5681</v>
       </c>
     </row>
     <row r="5">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="6">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.643</v>
+        <v>0.6519</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.6197</v>
+        <v>0.6026</v>
       </c>
     </row>
     <row r="8">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.6001</v>
+        <v>0.5998</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.6098</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="10">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.6068</v>
+        <v>0.6481</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.5995</v>
+        <v>0.5385</v>
       </c>
     </row>
   </sheetData>
@@ -721,7 +721,7 @@
         <v>0.2709</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6589</v>
+        <v>0.6775</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0.4155</v>
@@ -749,7 +749,7 @@
         <v>0.2424</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7493</v>
+        <v>0.7097</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0.4341</v>
@@ -774,10 +774,10 @@
         <v>0.6567</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8656</v>
+        <v>0.8651</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6129</v>
+        <v>0.5681</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0.0582</v>
@@ -805,7 +805,7 @@
         <v>0.997</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6597</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0.0012</v>
@@ -833,7 +833,7 @@
         <v>0.6582</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.643</v>
+        <v>0.6519</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0.1785</v>
@@ -861,7 +861,7 @@
         <v>0.9275</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6197</v>
+        <v>0.6026</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0.0369</v>
@@ -889,7 +889,7 @@
         <v>0.8631</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6001</v>
+        <v>0.5998</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0.0599</v>
@@ -917,7 +917,7 @@
         <v>0.3163</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6098</v>
+        <v>0.618</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0.3689</v>
@@ -945,7 +945,7 @@
         <v>0.2889</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6068</v>
+        <v>0.6481</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0.3976</v>
@@ -973,7 +973,7 @@
         <v>0.3678</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5995</v>
+        <v>0.5385</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0.3369</v>
@@ -1067,7 +1067,7 @@
         <v>0.2424</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7493</v>
+        <v>0.7097</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0.4341</v>
@@ -1095,7 +1095,7 @@
         <v>0.2709</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.6589</v>
+        <v>0.6775</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0.4155</v>
@@ -1123,7 +1123,7 @@
         <v>0.2889</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6068</v>
+        <v>0.6481</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0.3976</v>
@@ -1151,7 +1151,7 @@
         <v>0.3163</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6098</v>
+        <v>0.618</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0.3689</v>
@@ -1179,7 +1179,7 @@
         <v>0.3678</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5995</v>
+        <v>0.5385</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0.3369</v>
@@ -1207,7 +1207,7 @@
         <v>0.6582</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.643</v>
+        <v>0.6519</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0.1785</v>
@@ -1235,7 +1235,7 @@
         <v>0.8631</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6001</v>
+        <v>0.5998</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0.0599</v>
@@ -1260,10 +1260,10 @@
         <v>0.6567</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8656</v>
+        <v>0.8651</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6129</v>
+        <v>0.5681</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0.0582</v>
@@ -1291,7 +1291,7 @@
         <v>0.9275</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.6197</v>
+        <v>0.6026</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0.0369</v>
@@ -1319,7 +1319,7 @@
         <v>0.997</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6597</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0.0012</v>
@@ -1377,7 +1377,7 @@
         <v>-0.3207</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-3.2742</v>
+        <v>-1.1899</v>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
@@ -1391,7 +1391,7 @@
         <v>0.1498</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.4528</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
     </row>
@@ -1405,7 +1405,7 @@
         <v>-0.3366</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-3.8094</v>
+        <v>-1.2489</v>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>69.9803</v>
+        <v>67.384</v>
       </c>
     </row>
     <row r="6">
@@ -2092,13 +2092,13 @@
         <v>69.33</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6196</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.0109</v>
+        <v>1.0128</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>65.89</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         <v>69.26000000000001</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.4376</v>
+        <v>0.4331</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9787</v>
+        <v>0.9788</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>69.01000000000001</v>
+        <v>69.02</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2156,13 +2156,13 @@
         <v>62.9</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.5476</v>
+        <v>0.5369</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>72.13</v>
+        <v>72.08</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         <v>69.56</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5522</v>
+        <v>0.5396</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9993</v>
+        <v>0.9982</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>61.1</v>
+        <v>61.03</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>64.19</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.4859</v>
+        <v>0.4801</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.9874000000000001</v>
@@ -2252,13 +2252,13 @@
         <v>67.11</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6086</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.0101</v>
+        <v>1.0108</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>74.01000000000001</v>
+        <v>74.05</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         <v>67.06999999999999</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.4765</v>
+        <v>0.474</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9857</v>
+        <v>0.9863</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>64.25</v>
+        <v>64.28</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2316,13 +2316,13 @@
         <v>67.13</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.0147</v>
+        <v>1.0133</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>65.84</v>
+        <v>65.75</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -2348,13 +2348,13 @@
         <v>64.84</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.6384</v>
+        <v>0.6299</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.0148</v>
+        <v>1.0147</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>67.38</v>
+        <v>67.37</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>

--- a/output/problem2_stats.xlsx
+++ b/output/problem2_stats.xlsx
@@ -2095,10 +2095,10 @@
         <v>0.6196</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.0128</v>
+        <v>1.0383</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>66.01000000000001</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2127,10 +2127,10 @@
         <v>0.4331</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9788</v>
+        <v>0.9365</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>69.02</v>
+        <v>66.03</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         <v>0.5369</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9977</v>
+        <v>0.9932</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>72.08</v>
+        <v>71.75</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         <v>0.5396</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9982</v>
+        <v>0.9946</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>61.03</v>
+        <v>60.81</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         <v>0.4801</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66.81</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>0.6086</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.0108</v>
+        <v>1.0323</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>74.05</v>
+        <v>75.63</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         <v>0.474</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9863</v>
+        <v>0.9588</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>64.28</v>
+        <v>62.5</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         <v>0.6225000000000001</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.0133</v>
+        <v>1.0399</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>65.75</v>
+        <v>67.48</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         <v>0.6299</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.0147</v>
+        <v>1.044</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>67.37</v>
+        <v>69.31</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>

--- a/output/problem2_stats.xlsx
+++ b/output/problem2_stats.xlsx
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1370,105 +1370,77 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>逻辑连词总频次</t>
+          <t>内容字符数</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.3207</v>
+        <v>0.3907</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-1.1899</v>
+        <v>1.4495</v>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>规范编号公式占比</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.5558999999999999</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>截距</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>67.384</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>参考文献数量</t>
+          <t>样本内R²/RMSE/MAE</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.3366</v>
+        <v>0.1866</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-1.2489</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+        <v>0.9019</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.7798</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>截距</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
+          <t>LOO-CV R²/RMSE/MAE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-0.4713</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4.5001</v>
+      </c>
       <c r="D5" s="2" t="n">
-        <v>67.384</v>
+        <v>3.8585</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>样本内R²/RMSE/MAE</t>
+          <t>OLS LOO-CV R²</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2672</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.6894</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>LOO-CV R²/RMSE/MAE</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>-0.9193</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>5.1398</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>4.2737</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>OLS LOO-CV R²</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>-1.0967</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+        <v>-0.5135</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>（对比）</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1528,13 +1500,13 @@
         <v>65.18000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>69.53</v>
+        <v>70.09</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>69.33</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-4.15</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="3">
@@ -1547,13 +1519,13 @@
         <v>70.51000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>66.38</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>69.26000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.24</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="4">
@@ -1566,13 +1538,13 @@
         <v>72.23999999999999</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>62.34</v>
+        <v>64.28</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>62.9</v>
+        <v>64.56</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.34</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="5">
@@ -1585,13 +1557,13 @@
         <v>61.14</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>69.72</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>69.56</v>
+        <v>67.19</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-8.41</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="6">
@@ -1604,13 +1576,13 @@
         <v>67.66</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>63.3</v>
+        <v>67.36</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>64.19</v>
+        <v>67.36</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.47</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -1623,13 +1595,13 @@
         <v>73.26000000000001</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>67.18000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>67.11</v>
+        <v>67.23</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.16</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="8">
@@ -1642,13 +1614,13 @@
         <v>65.18000000000001</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>66.92</v>
+        <v>67.22</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>67.06999999999999</v>
+        <v>67.27</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-1.89</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="9">
@@ -1661,13 +1633,13 @@
         <v>64.89</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>67.22</v>
+        <v>66.25</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>67.13</v>
+        <v>66.41</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2.24</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="10">
@@ -1680,13 +1652,13 @@
         <v>66.39</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>64.42</v>
+        <v>68.92</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>64.84</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.56</v>
+        <v>-2.37</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1740,58 +1712,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>逻辑连词总频次</t>
+          <t>内容字符数</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.2136</v>
+        <v>0.2926</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.8472</v>
+        <v>-0.5712</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.491</v>
+        <v>0.831</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3831</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>规范编号公式占比</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.08069999999999999</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>-0.6096</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.3121</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>参考文献数量</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>-0.2683</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>-0.8953</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.6111</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.3553</v>
+        <v>0.3765</v>
       </c>
     </row>
   </sheetData>
@@ -1805,14 +1739,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1823,20 +1755,10 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>β(逻辑连词总频次)变化%</t>
+          <t>β(内容字符数)变化%</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>β(规范编号公式占比)变化%</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>β(参考文献数量)变化%</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>最大变化%</t>
         </is>
@@ -1849,16 +1771,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>31.1</v>
+        <v>26.5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>31.1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="3">
@@ -1868,16 +1784,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>18.3</v>
+        <v>11.9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>18.3</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="4">
@@ -1887,16 +1797,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>103.2</v>
+        <v>58.4</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>128.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="5">
@@ -1906,16 +1810,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>92.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="6">
@@ -1925,16 +1823,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>16.7</v>
+        <v>1.2</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -1944,16 +1836,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>47.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>186.2</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>186.2</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1963,16 +1849,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>35.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1982,16 +1862,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>35.1</v>
+        <v>11.2</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="10">
@@ -2001,16 +1875,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>47.6</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +1957,7 @@
         <v>65.18000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>69.33</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.6196</v>
@@ -2121,7 +1989,7 @@
         <v>70.51000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>69.26000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.4331</v>
@@ -2153,7 +2021,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>62.9</v>
+        <v>64.56</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.5369</v>
@@ -2185,7 +2053,7 @@
         <v>61.14</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>69.56</v>
+        <v>67.19</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.5396</v>
@@ -2217,7 +2085,7 @@
         <v>67.66</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>64.19</v>
+        <v>67.36</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.4801</v>
@@ -2249,7 +2117,7 @@
         <v>73.26000000000001</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>67.11</v>
+        <v>67.23</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.6086</v>
@@ -2281,7 +2149,7 @@
         <v>65.18000000000001</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>67.06999999999999</v>
+        <v>67.27</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.474</v>
@@ -2313,7 +2181,7 @@
         <v>64.89</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>67.13</v>
+        <v>66.41</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.6225000000000001</v>
@@ -2345,7 +2213,7 @@
         <v>66.39</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>64.84</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.6299</v>
